--- a/output/Tables/Sensitivity analyses/HIA_speed_sensitivity_1000replicate.xlsx
+++ b/output/Tables/Sensitivity analyses/HIA_speed_sensitivity_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,36 @@
           <t>tot_daly_up</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -398,22 +428,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>59660.605</v>
+        <v>56725.347</v>
       </c>
       <c r="C2">
-        <v>56745.513</v>
+        <v>53927.56</v>
       </c>
       <c r="D2">
-        <v>62572.013</v>
+        <v>59524.445</v>
       </c>
       <c r="E2">
-        <v>618896.4300000001</v>
+        <v>597701.209</v>
       </c>
       <c r="F2">
-        <v>600855.507</v>
+        <v>579960.536</v>
       </c>
       <c r="G2">
-        <v>636967.492</v>
+        <v>615548.9449999999</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>79496311334.59</v>
+      </c>
+      <c r="L2">
+        <v>77123868309.586</v>
+      </c>
+      <c r="M2">
+        <v>81867886157.66299</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>41535.109</v>
+        <v>38920.233</v>
       </c>
       <c r="C3">
-        <v>39752.138</v>
+        <v>37190.925</v>
       </c>
       <c r="D3">
-        <v>43322.613</v>
+        <v>40647.787</v>
       </c>
       <c r="E3">
-        <v>37217.811</v>
+        <v>53548.54</v>
       </c>
       <c r="F3">
-        <v>35769.643</v>
+        <v>51407.52</v>
       </c>
       <c r="G3">
-        <v>38677.469</v>
+        <v>55696.982</v>
+      </c>
+      <c r="H3">
+        <v>2050685684.885</v>
+      </c>
+      <c r="I3">
+        <v>1960678950.147</v>
+      </c>
+      <c r="J3">
+        <v>2142073421.443</v>
+      </c>
+      <c r="K3">
+        <v>7122583810.875</v>
+      </c>
+      <c r="L3">
+        <v>6837768444.19</v>
+      </c>
+      <c r="M3">
+        <v>7407828488.843</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>6651.525</v>
+        <v>6255.526</v>
       </c>
       <c r="C4">
-        <v>6367.072</v>
+        <v>5978.933</v>
       </c>
       <c r="D4">
-        <v>6940.507</v>
+        <v>6536.72</v>
       </c>
       <c r="E4">
-        <v>12983.07</v>
+        <v>11314.213</v>
       </c>
       <c r="F4">
-        <v>12407.649</v>
+        <v>10771.025</v>
       </c>
       <c r="G4">
-        <v>13575.486</v>
+        <v>11868.83</v>
+      </c>
+      <c r="H4">
+        <v>245236185.141</v>
+      </c>
+      <c r="I4">
+        <v>234363355.338</v>
+      </c>
+      <c r="J4">
+        <v>256303094.291</v>
+      </c>
+      <c r="K4">
+        <v>1504687231.692</v>
+      </c>
+      <c r="L4">
+        <v>1432669286.296</v>
+      </c>
+      <c r="M4">
+        <v>1578310068.143</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>14184.764</v>
+        <v>13073.323</v>
       </c>
       <c r="C5">
-        <v>13338.114</v>
+        <v>12264.934</v>
       </c>
       <c r="D5">
-        <v>15034.817</v>
+        <v>13886.743</v>
       </c>
       <c r="E5">
-        <v>23916.562</v>
+        <v>14905.589</v>
       </c>
       <c r="F5">
-        <v>22754.241</v>
+        <v>13968.035</v>
       </c>
       <c r="G5">
-        <v>25093.484</v>
+        <v>15854.792</v>
+      </c>
+      <c r="H5">
+        <v>217610446.108</v>
+      </c>
+      <c r="I5">
+        <v>204220909.802</v>
+      </c>
+      <c r="J5">
+        <v>231116894.712</v>
+      </c>
+      <c r="K5">
+        <v>1982256796.109</v>
+      </c>
+      <c r="L5">
+        <v>1857727035.619</v>
+      </c>
+      <c r="M5">
+        <v>2108419821.331</v>
       </c>
     </row>
     <row r="6">
@@ -498,47 +600,83 @@
         </is>
       </c>
       <c r="B6">
-        <v>148348.444</v>
+        <v>138276.783</v>
       </c>
       <c r="C6">
-        <v>142876.164</v>
+        <v>133110.696</v>
       </c>
       <c r="D6">
-        <v>153854.153</v>
+        <v>143445.835</v>
       </c>
       <c r="E6">
-        <v>47995.882</v>
+        <v>52188.648</v>
       </c>
       <c r="F6">
-        <v>45551.615</v>
+        <v>49653.786</v>
       </c>
       <c r="G6">
-        <v>50493.113</v>
+        <v>54735.983</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>6940342809.814</v>
+      </c>
+      <c r="L6">
+        <v>6604961469.536</v>
+      </c>
+      <c r="M6">
+        <v>7278211807.142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>Chronic diseases</t>
         </is>
       </c>
       <c r="B7">
-        <v>210719.842</v>
+        <v>196525.865</v>
       </c>
       <c r="C7">
-        <v>202333.488</v>
+        <v>188545.488</v>
       </c>
       <c r="D7">
-        <v>219152.09</v>
+        <v>204517.085</v>
       </c>
       <c r="E7">
-        <v>122113.325</v>
+        <v>131956.99</v>
       </c>
       <c r="F7">
-        <v>116483.148</v>
+        <v>125800.366</v>
       </c>
       <c r="G7">
-        <v>127839.552</v>
+        <v>138156.587</v>
+      </c>
+      <c r="H7">
+        <v>2513532316.134</v>
+      </c>
+      <c r="I7">
+        <v>2399263215.287</v>
+      </c>
+      <c r="J7">
+        <v>2629493410.446</v>
+      </c>
+      <c r="K7">
+        <v>17549870648.49</v>
+      </c>
+      <c r="L7">
+        <v>16733126235.641</v>
+      </c>
+      <c r="M7">
+        <v>18372770185.459</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>270380.447</v>
+        <v>253251.212</v>
       </c>
       <c r="C8">
-        <v>259079.001</v>
+        <v>242473.048</v>
       </c>
       <c r="D8">
-        <v>281724.103</v>
+        <v>264041.53</v>
       </c>
       <c r="E8">
-        <v>741009.755</v>
+        <v>729658.1990000001</v>
       </c>
       <c r="F8">
-        <v>717338.655</v>
+        <v>705760.902</v>
       </c>
       <c r="G8">
-        <v>764807.0440000001</v>
+        <v>753705.5319999999</v>
+      </c>
+      <c r="H8">
+        <v>2513532316.134</v>
+      </c>
+      <c r="I8">
+        <v>2399263215.287</v>
+      </c>
+      <c r="J8">
+        <v>2629493410.446</v>
+      </c>
+      <c r="K8">
+        <v>97046181983.07999</v>
+      </c>
+      <c r="L8">
+        <v>93856994545.22701</v>
+      </c>
+      <c r="M8">
+        <v>100240656343.122</v>
       </c>
     </row>
   </sheetData>
